--- a/Collections/EURO/Vatican_city/#EURO#Vatican_city#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Vatican_city/#EURO#Vatican_city#Regular#[2002-present]#circulation_quality.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Vatican_city\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2860B684-7896-45BC-BD6B-515CA16DBB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF09B42D-2C28-4332-8306-8ACF16F358AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -388,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="72">
   <si>
     <t>Year</t>
   </si>
@@ -573,6 +576,39 @@
   <si>
     <t>Subtype_2#Map_of_Europe</t>
   </si>
+  <si>
+    <t>33.000</t>
+  </si>
+  <si>
+    <t>49.799</t>
+  </si>
+  <si>
+    <t>50.299</t>
+  </si>
+  <si>
+    <t>50.999</t>
+  </si>
+  <si>
+    <t>74.930</t>
+  </si>
+  <si>
+    <t>1.919.715</t>
+  </si>
+  <si>
+    <t>1.946.210</t>
+  </si>
+  <si>
+    <t>1.697.432</t>
+  </si>
+  <si>
+    <t>1.867.539</t>
+  </si>
+  <si>
+    <t>129.799</t>
+  </si>
+  <si>
+    <t>121.799</t>
+  </si>
 </sst>
 </file>
 
@@ -581,7 +617,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ [$€-1];[Red]\-#,##0\ [$€-1]"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -643,6 +679,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -889,10 +929,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -901,15 +941,14 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="27">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1023,6 +1062,87 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1054,9 +1174,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="25" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1325,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1792,18 +1912,151 @@
         <v/>
       </c>
     </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:F21">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="F3:F27">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F21">
+  <conditionalFormatting sqref="F3:F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1823,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2280,13 +2533,145 @@
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="22" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2296,12 +2681,13 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:F21">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="F3:F27">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F21">
+  <conditionalFormatting sqref="F3:F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2321,7 +2707,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2778,13 +3164,145 @@
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="22" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2794,12 +3312,13 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:F4 F12:F21">
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="F3:F4 F12:F27">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F4 F12:F21">
+  <conditionalFormatting sqref="F3:F4 F12:F27">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2812,7 +3331,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F11">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2836,7 +3355,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2855,7 +3374,7 @@
       <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
@@ -2865,7 +3384,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>57</v>
       </c>
@@ -3338,6 +3857,150 @@
       </c>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3348,11 +4011,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F4 F12:F21">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F4 F12:F21">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3364,12 +4061,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+  <conditionalFormatting sqref="F25:F27">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
+  <conditionalFormatting sqref="F25:F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3389,7 +4086,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3408,7 +4105,7 @@
       <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
@@ -3418,7 +4115,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>57</v>
       </c>
@@ -3891,6 +4588,150 @@
       </c>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3901,11 +4742,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F4 F12:F21">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F4 F12:F21">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3917,12 +4792,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+  <conditionalFormatting sqref="F25:F27">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
+  <conditionalFormatting sqref="F25:F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3942,7 +4817,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3961,7 +4836,7 @@
       <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
@@ -3971,7 +4846,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>57</v>
       </c>
@@ -4444,6 +5319,146 @@
       </c>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="22"/>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="22"/>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4454,11 +5469,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F4 F12:F21">
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F4 F12:F21">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4470,12 +5519,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+  <conditionalFormatting sqref="F25:F27">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
+  <conditionalFormatting sqref="F25:F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4495,7 +5544,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4514,7 +5563,7 @@
       <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
@@ -4524,7 +5573,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>57</v>
       </c>
@@ -4998,6 +6047,148 @@
       </c>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="22"/>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -5008,11 +6199,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F4 F12:F21">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F4 F12:F21">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5024,12 +6249,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+  <conditionalFormatting sqref="F25:F27">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
+  <conditionalFormatting sqref="F25:F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5049,7 +6274,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5068,7 +6293,7 @@
       <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
@@ -5078,7 +6303,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="26" t="s">
         <v>57</v>
       </c>
@@ -5553,6 +6778,148 @@
       </c>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" ref="G22:G27" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2023</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="22"/>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -5564,11 +6931,45 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F4 F12:F21">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F4 F12:F21">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F24">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5580,12 +6981,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+  <conditionalFormatting sqref="F25:F27">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11">
+  <conditionalFormatting sqref="F25:F27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
